--- a/Collections/EURO/Belgium/#EURO#Belgium#Regular#[1999-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Belgium/#EURO#Belgium#Regular#[1999-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Belgium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9544140E-FA11-4BCE-9153-A83742915ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFA0A4E-8679-4C0E-80A3-96E771B89D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -644,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="170">
   <si>
     <t>-</t>
   </si>
@@ -1138,6 +1141,24 @@
   </si>
   <si>
     <t>Subtype_4#Special_distinctions_1</t>
+  </si>
+  <si>
+    <t>8.500</t>
+  </si>
+  <si>
+    <t>6.500</t>
+  </si>
+  <si>
+    <t>7.500</t>
+  </si>
+  <si>
+    <t>13.906.500</t>
+  </si>
+  <si>
+    <t>7.507.500</t>
+  </si>
+  <si>
+    <t>3.206.500</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1527,359 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="98">
+  <dxfs count="142">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2307,9 +2680,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="45" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2578,7 +2951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3436,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H28" s="25" t="s">
         <v>0</v>
@@ -3446,6 +3819,66 @@
       </c>
       <c r="J28" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="str">
+        <f t="shared" ref="J29:J30" si="2">IF(OR(AND(H29&gt;1,H29&lt;&gt;"-"),AND(I29&gt;1,I29&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" s="26"/>
+      <c r="H30" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3459,12 +3892,12 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="H23:H24">
-    <cfRule type="containsText" dxfId="97" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:H24">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3476,11 +3909,79 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3 H6 H8:H9 H11:H12 H20:H22 H14:H18">
-    <cfRule type="containsText" dxfId="96" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3 H6 H8:H9 H11:H12 H20:H22 H14:H18">
+  <conditionalFormatting sqref="H6 H3 H8:H9 H11:H12 H20:H22 H14:H18">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="containsText" dxfId="139" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="containsText" dxfId="138" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="containsText" dxfId="137" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="136" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3492,12 +3993,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="95" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="135" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3509,46 +4010,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="94" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="containsText" dxfId="93" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="92" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H25:H28">
+    <cfRule type="containsText" dxfId="134" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H28">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3560,12 +4027,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="91" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
+  <conditionalFormatting sqref="I3:I28">
+    <cfRule type="containsText" dxfId="133" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I28">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3577,12 +4044,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H28">
-    <cfRule type="containsText" dxfId="90" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H28">
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="132" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3594,12 +4061,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I28">
-    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I28">
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="43" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3611,12 +4078,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="42" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="containsText" dxfId="41" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30">
+    <cfRule type="containsText" dxfId="40" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3636,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4431,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>0</v>
@@ -4441,6 +4942,64 @@
       </c>
       <c r="I27" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="str">
+        <f t="shared" ref="I28:I29" si="2">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-"),AND(H28&gt;1,H28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F29" s="26"/>
+      <c r="G29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4454,12 +5013,12 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="87" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -4471,11 +5030,79 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4 G7:G8 G10:G11 G13:G14 G16:G20">
-    <cfRule type="containsText" dxfId="86" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G8 G4 G10:G11 G13:G14 G16:G20">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="129" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="128" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="containsText" dxfId="127" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="containsText" dxfId="126" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4487,12 +5114,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="85" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="G12">
+    <cfRule type="containsText" dxfId="125" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4504,12 +5131,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
+  <conditionalFormatting sqref="G15">
+    <cfRule type="containsText" dxfId="124" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4521,12 +5148,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="83" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
+  <conditionalFormatting sqref="G21">
+    <cfRule type="containsText" dxfId="123" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G21">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4538,12 +5165,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
-    <cfRule type="containsText" dxfId="82" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
+  <conditionalFormatting sqref="G22">
+    <cfRule type="containsText" dxfId="122" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4555,29 +5182,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="containsText" dxfId="81" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="80" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
+  <conditionalFormatting sqref="G24:G27">
+    <cfRule type="containsText" dxfId="121" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:G27">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4589,12 +5199,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
-    <cfRule type="containsText" dxfId="79" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
+  <conditionalFormatting sqref="H3:H27">
+    <cfRule type="containsText" dxfId="120" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H27">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4606,29 +5216,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="containsText" dxfId="78" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G27">
-    <cfRule type="containsText" dxfId="77" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G27">
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4640,12 +5233,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H27">
-    <cfRule type="containsText" dxfId="76" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H27">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4657,6 +5250,40 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4665,7 +5292,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5473,6 +6100,64 @@
         <v/>
       </c>
     </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="str">
+        <f t="shared" ref="I28:I29" si="2">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-"),AND(H28&gt;1,H28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F29" s="26"/>
+      <c r="G29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="4">
@@ -5483,11 +6168,198 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="75" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3 G7:G10 G14:G21 H22:H23">
+    <cfRule type="containsText" dxfId="118" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G10 G3 G14:G21 H22:H23">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="117" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="116" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="containsText" dxfId="115" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="containsText" dxfId="114" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="containsText" dxfId="113" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:G27">
+    <cfRule type="containsText" dxfId="112" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:G27">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H21">
+    <cfRule type="containsText" dxfId="111" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H21">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="containsText" dxfId="110" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23">
+    <cfRule type="containsText" dxfId="109" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24:H25">
+    <cfRule type="containsText" dxfId="108" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24:H25">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5499,13 +6371,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3 G7:G10 G14:G21 H22:H23">
-    <cfRule type="containsText" dxfId="74" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G10 G3 G14:G21 H22:H23">
-    <cfRule type="colorScale" priority="30">
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="107" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -5516,97 +6388,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="73" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="72" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="71" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="70" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="containsText" dxfId="69" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G27">
-    <cfRule type="containsText" dxfId="68" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G27">
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="106" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5618,12 +6405,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H21">
-    <cfRule type="containsText" dxfId="67" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H21">
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="35" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5635,12 +6422,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="containsText" dxfId="66" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="34" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5652,46 +6439,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="65" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H25">
-    <cfRule type="containsText" dxfId="64" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H25">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="63" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
+  <conditionalFormatting sqref="G29">
+    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5703,12 +6456,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="62" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5728,7 +6481,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -6601,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>0</v>
@@ -6611,6 +7364,70 @@
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="str">
+        <f t="shared" ref="J28:J29" si="2">IF(OR(AND(H28&gt;1,H28&lt;&gt;"-"),AND(I28&gt;1,I28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -6624,11 +7441,249 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="H20">
-    <cfRule type="containsText" dxfId="61" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3 H5 H8:H9 H19 H14:H17 H21 I22:I23">
+    <cfRule type="containsText" dxfId="104" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5 H3 H8:H9 H19 H14:H17 H21 I22:I23">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="103" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="containsText" dxfId="102" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="containsText" dxfId="101" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="containsText" dxfId="100" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="99" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="98" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="97" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="containsText" dxfId="96" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
+    <cfRule type="containsText" dxfId="95" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="containsText" dxfId="94" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24:H27">
+    <cfRule type="containsText" dxfId="93" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24:H27">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24:I26">
+    <cfRule type="containsText" dxfId="92" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24:I26">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I21">
+    <cfRule type="containsText" dxfId="91" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I21">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6640,13 +7695,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3 H5 H8:H9 H19 H14:H17 H21 I22:I23">
-    <cfRule type="containsText" dxfId="60" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3 H5 H8:H9 H19 H14:H17 H21 I22:I23">
-    <cfRule type="colorScale" priority="34">
+  <conditionalFormatting sqref="I27">
+    <cfRule type="containsText" dxfId="90" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I27">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -6657,165 +7712,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="59" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="58" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="57" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="containsText" dxfId="56" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="55" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="54" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="53" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="containsText" dxfId="52" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="containsText" dxfId="51" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="containsText" dxfId="50" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6827,12 +7729,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H27">
-    <cfRule type="containsText" dxfId="49" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H27">
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="29" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6844,29 +7746,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:I26">
-    <cfRule type="containsText" dxfId="48" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I24:I26">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I21">
-    <cfRule type="containsText" dxfId="47" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I21">
+  <conditionalFormatting sqref="I28">
+    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6878,12 +7763,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I27">
-    <cfRule type="containsText" dxfId="46" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I27">
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6903,7 +7788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -7818,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="3" t="str">
-        <f t="shared" ref="K27:K28" si="2">IF(OR(AND(I27&gt;1,I27&lt;&gt;"-"),AND(J27&gt;1,J27&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="K27:K30" si="2">IF(OR(AND(I27&gt;1,I27&lt;&gt;"-"),AND(J27&gt;1,J27&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -7852,6 +8737,72 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="H30" s="26"/>
+      <c r="I30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -7865,11 +8816,147 @@
     <mergeCell ref="I1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="I18:I23">
-    <cfRule type="containsText" dxfId="45" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I23">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4 I6 I8:I17 J24">
+    <cfRule type="containsText" dxfId="88" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6 I4 I8:I17 J24">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="containsText" dxfId="87" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="containsText" dxfId="86" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24">
+    <cfRule type="containsText" dxfId="85" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25">
+    <cfRule type="containsText" dxfId="84" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25">
+    <cfRule type="containsText" dxfId="83" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J23">
+    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="containsText" dxfId="81" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7881,13 +8968,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4 I6 I8:I17 J24">
-    <cfRule type="containsText" dxfId="44" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4 I6 I8:I17 J24">
-    <cfRule type="colorScale" priority="30">
+  <conditionalFormatting sqref="I26:I28">
+    <cfRule type="containsText" dxfId="80" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:I28">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7898,13 +8985,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="43" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="colorScale" priority="28">
+  <conditionalFormatting sqref="J26:J27">
+    <cfRule type="containsText" dxfId="79" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26:J27">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7915,13 +9002,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="42" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="colorScale" priority="26">
+  <conditionalFormatting sqref="J28">
+    <cfRule type="containsText" dxfId="78" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7932,80 +9019,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24">
-    <cfRule type="containsText" dxfId="41" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I24">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I25">
-    <cfRule type="containsText" dxfId="40" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I25">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
-    <cfRule type="containsText" dxfId="39" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J23">
-    <cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J23">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8017,12 +9036,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I28">
-    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I28">
+  <conditionalFormatting sqref="J29">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J29">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8034,12 +9053,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J26:J27">
-    <cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J26:J27">
+  <conditionalFormatting sqref="I30">
+    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8051,12 +9070,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
+  <conditionalFormatting sqref="J30">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J30">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8076,7 +9095,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -8892,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="str">
-        <f t="shared" ref="J25:J27" si="1">IF(OR(AND(H25&gt;1,H25&lt;&gt;"-"),AND(I25&gt;1,I25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J25:J28" si="1">IF(OR(AND(H25&gt;1,H25&lt;&gt;"-"),AND(I25&gt;1,I25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -8959,6 +9978,70 @@
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="str">
+        <f t="shared" ref="J28:J29" si="2">IF(OR(AND(H29&gt;1,H29&lt;&gt;"-"),AND(I29&gt;1,I29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -8972,12 +10055,12 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="33" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -8989,11 +10072,113 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8 H6 H15:H16 H3 H18:H21 H11:H13 I23">
-    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8 H6 H15:H16 H3 H18:H21 H11:H13 I23">
+  <conditionalFormatting sqref="H6 H8 H15:H16 H3 H18:H21 H11:H13 I23">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="75" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="containsText" dxfId="74" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="containsText" dxfId="73" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="containsText" dxfId="72" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="containsText" dxfId="71" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:I22 I3:I21">
+    <cfRule type="containsText" dxfId="70" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:I22 I3:I21">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9005,12 +10190,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="31" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
+  <conditionalFormatting sqref="H17">
+    <cfRule type="containsText" dxfId="69" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9022,13 +10207,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="30" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="colorScale" priority="22">
+  <conditionalFormatting sqref="I24:I27">
+    <cfRule type="containsText" dxfId="68" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24:I27">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -9039,29 +10224,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="29" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9">
-    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9">
+  <conditionalFormatting sqref="H24:H27">
+    <cfRule type="containsText" dxfId="67" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24:H27">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9073,29 +10241,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I22 I3:I21">
-    <cfRule type="containsText" dxfId="26" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I22 I3:I21">
+  <conditionalFormatting sqref="H23">
+    <cfRule type="containsText" dxfId="66" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9107,13 +10258,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -9124,12 +10275,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:I27">
-    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I24:I27">
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9141,29 +10309,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H27">
-    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H27">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9183,7 +10334,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -10055,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>0</v>
@@ -10065,6 +11216,70 @@
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="str">
+        <f t="shared" ref="J28" si="2">IF(OR(AND(H28&gt;1,H28&lt;&gt;"-"),AND(I28&gt;1,I28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="str">
+        <f t="shared" ref="J29" si="3">IF(OR(AND(H29&gt;1,H29&lt;&gt;"-"),AND(I29&gt;1,I29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -10078,11 +11293,164 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="H17:H23">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17:H23">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6:H8 H15:H16 H12:H13 H3">
+    <cfRule type="containsText" dxfId="64" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6:H8 H15:H16 H12:H13 H3">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="63" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="containsText" dxfId="62" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="containsText" dxfId="61" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="containsText" dxfId="60" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="59" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="58" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I23 H24:I27">
+    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I23 H24:I27">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28:I28">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28:I28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10094,131 +11462,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H6:H8 H15:H16 H12:H13 H3">
-    <cfRule type="containsText" dxfId="20" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6:H8 H15:H16 H12:H13 H3">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9">
-    <cfRule type="containsText" dxfId="17" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I23 H24:I27">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I23 H24:I27">
+  <conditionalFormatting sqref="H29:I29">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29:I29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11183,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>0</v>
@@ -11193,6 +12442,72 @@
       </c>
       <c r="K28" s="3" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="str">
+        <f t="shared" ref="K29:K30" si="3">IF(OR(AND(I29&gt;1,I29&lt;&gt;"-"),AND(J29&gt;1,J29&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="H30" s="26"/>
+      <c r="I30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11214,11 +12529,113 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="I17:I22 I23:J23">
-    <cfRule type="containsText" dxfId="12" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17:I22 I23:J23">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4 I6:I12 I14:I16 J24">
+    <cfRule type="containsText" dxfId="55" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:I12 I4 I14:I16 J24">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:J3 J4:J22">
+    <cfRule type="containsText" dxfId="54" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:J3 J4:J22">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="containsText" dxfId="53" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="containsText" dxfId="52" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25">
+    <cfRule type="containsText" dxfId="51" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25">
+    <cfRule type="containsText" dxfId="50" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11230,63 +12647,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4 I6:I12 I14:I16 J24">
-    <cfRule type="containsText" dxfId="11" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:I12 I4 I14:I16 J24">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:J3 J4:J22">
-    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:J3 J4:J22">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
+  <conditionalFormatting sqref="I24">
+    <cfRule type="containsText" dxfId="49" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11298,12 +12664,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I25">
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I25">
+  <conditionalFormatting sqref="I26:I28">
+    <cfRule type="containsText" dxfId="48" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:I28">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26:J28">
+    <cfRule type="containsText" dxfId="47" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26:J28">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11315,12 +12698,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11332,12 +12715,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I24">
+  <conditionalFormatting sqref="J29">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J29">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11349,12 +12732,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I28">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I28">
+  <conditionalFormatting sqref="I30">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11366,12 +12749,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J26:J28">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J26:J28">
+  <conditionalFormatting sqref="J30">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J30">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
